--- a/results/result.xlsx
+++ b/results/result.xlsx
@@ -390,10 +390,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>10489</v>
+        <v>40162</v>
       </c>
       <c r="B2">
-        <v>0.3966</v>
+        <v>0.4207</v>
       </c>
     </row>
   </sheetData>

--- a/results/result.xlsx
+++ b/results/result.xlsx
@@ -390,10 +390,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>40162</v>
+        <v>31254</v>
       </c>
       <c r="B2">
-        <v>0.4207</v>
+        <v>0.3913</v>
       </c>
     </row>
   </sheetData>

--- a/results/result.xlsx
+++ b/results/result.xlsx
@@ -390,10 +390,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>31254</v>
+        <v>30939</v>
       </c>
       <c r="B2">
-        <v>0.3913</v>
+        <v>0.3996</v>
       </c>
     </row>
   </sheetData>

--- a/results/result.xlsx
+++ b/results/result.xlsx
@@ -390,10 +390,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>30939</v>
+        <v>31254</v>
       </c>
       <c r="B2">
-        <v>0.3996</v>
+        <v>0.4138</v>
       </c>
     </row>
   </sheetData>
